--- a/02-cascade-civic-rev5-ato/artifacts/poam.xlsx
+++ b/02-cascade-civic-rev5-ato/artifacts/poam.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="R9" s="24" t="n"/>
     </row>
-    <row r="10" ht="68.65000000000001" customHeight="1" s="18">
+    <row r="10" ht="260" customHeight="1" s="18">
       <c r="A10" s="24" t="inlineStr">
         <is>
           <t>V-006</t>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="N10" s="24" t="inlineStr">
         <is>
-          <t>M1: Develop tabletop scenario (2026-05-01); M2: Execute tabletop with Legal and Communications (2026-06-01); M3: Update IR Plan and roster (2026-06-15)</t>
+          <t>M1: Develop tabletop scenario (2026-05-01); M2: Execute tabletop with Legal and Communications (2026-06-01); M3: Update IR Plan and roster (2026-06-15) Later evidence (AAR approved 2026-06-04, sections 8–11): original 2026-06-15 completion is incompatible with corrective actions due 2026-06-30 and 2026-07-15. Reason: notification draft took 64 minutes against 60; severity classification was delayed. Follow-up exercise recommended by 2026-09-30. Original date retained; approved revised closure date not recorded.</t>
         </is>
       </c>
       <c r="O10" s="24" t="inlineStr">

--- a/02-cascade-civic-rev5-ato/artifacts/poam.xlsx
+++ b/02-cascade-civic-rev5-ato/artifacts/poam.xlsx
@@ -939,7 +939,7 @@
       </c>
       <c r="J7" s="24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K7" s="24" t="inlineStr">
